--- a/Gravedigger2026/Assets/ConfigTables/Excel/战斗_技能效果配置表_Combat_SkillEffectConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/战斗_技能效果配置表_Combat_SkillEffectConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,6 @@
           <t>SkillEffect_01</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -466,7 +465,6 @@
           <t>SkillEffect_02</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -474,7 +472,6 @@
           <t>SkillEffect_03</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -482,7 +479,6 @@
           <t>SkillEffect_04</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -490,7 +486,6 @@
           <t>SkillEffect_05</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -498,7 +493,6 @@
           <t>SkillEffect_06</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -506,7 +500,6 @@
           <t>SkillEffect_07</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -514,7 +507,6 @@
           <t>SkillEffect_08</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -522,7 +514,6 @@
           <t>SkillEffect_09</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -530,7 +521,18 @@
           <t>SkillEffect_10</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>BondEffect_Demo_1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Mode1 演示羁绊：展示占位（Handler 未接线）</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Gravedigger2026/Assets/ConfigTables/Excel/战斗_技能效果配置表_Combat_SkillEffectConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/战斗_技能效果配置表_Combat_SkillEffectConfig.xlsx
@@ -458,6 +458,7 @@
           <t>SkillEffect_01</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -465,6 +466,7 @@
           <t>SkillEffect_02</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -472,6 +474,7 @@
           <t>SkillEffect_03</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -479,6 +482,7 @@
           <t>SkillEffect_04</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -486,6 +490,7 @@
           <t>SkillEffect_05</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -493,6 +498,7 @@
           <t>SkillEffect_06</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -500,6 +506,7 @@
           <t>SkillEffect_07</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -507,6 +514,7 @@
           <t>SkillEffect_08</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -514,6 +522,7 @@
           <t>SkillEffect_09</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -521,6 +530,7 @@
           <t>SkillEffect_10</t>
         </is>
       </c>
+      <c r="B13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
